--- a/data/inventario_actual.xlsx
+++ b/data/inventario_actual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Riviere\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C63ED969-D6A9-46B5-9A78-73BE9DB1B319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F269314D-C1D1-41BE-A0AB-DF39769C73F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22416" yWindow="624" windowWidth="21600" windowHeight="10728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="145">
   <si>
     <t>Estilo</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>Estado</t>
-  </si>
-  <si>
     <t>Estilo C12-125B</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>LM27</t>
   </si>
   <si>
-    <t>1U VENDIDA</t>
-  </si>
-  <si>
     <t>Estilo C13-18D</t>
   </si>
   <si>
@@ -210,9 +204,6 @@
     <t>Blanco</t>
   </si>
   <si>
-    <t>Estilo S07 NEGRA</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
@@ -339,9 +330,6 @@
     <t>Estilo S13-140C</t>
   </si>
   <si>
-    <t>VENDIDA</t>
-  </si>
-  <si>
     <t>Estilo S13-38</t>
   </si>
   <si>
@@ -438,12 +426,6 @@
     <t>Estilo SP11-64</t>
   </si>
   <si>
-    <t>PÉRDIDA</t>
-  </si>
-  <si>
-    <t>(NO PAGÓ)</t>
-  </si>
-  <si>
     <t>DISEÑO</t>
   </si>
   <si>
@@ -492,7 +474,7 @@
     <t>TOTAL:</t>
   </si>
   <si>
-    <t>Vendida</t>
+    <t>Estilo S07-NEGRA</t>
   </si>
 </sst>
 </file>
@@ -974,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14017989-1FAB-C241-8952-AFE7282E7826}">
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -983,11 +965,9 @@
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13.140625" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,161 +995,143 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="I2">
         <v>349000</v>
       </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="I3">
         <v>379000</v>
       </c>
-      <c r="L3" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I4">
         <v>379000</v>
       </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="I5">
         <v>379000</v>
       </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>379000</v>
       </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1178,56 +1140,50 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <v>379000</v>
       </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8">
         <v>379000</v>
       </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1236,120 +1192,102 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9">
         <v>379000</v>
       </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10">
         <v>379000</v>
       </c>
-      <c r="J10" t="s">
-        <v>150</v>
-      </c>
-      <c r="L10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="I11" s="5">
         <v>399000</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="I12">
         <v>399000</v>
       </c>
-      <c r="L12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1358,27 +1296,24 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13">
         <v>399000</v>
       </c>
-      <c r="L13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1387,111 +1322,93 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="I14">
         <v>399000</v>
       </c>
-      <c r="J14" t="s">
-        <v>150</v>
-      </c>
-      <c r="L14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="9">
         <v>2</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I15" s="9">
         <v>399000</v>
       </c>
-      <c r="J15" s="9" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="H16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I16">
         <v>459000</v>
       </c>
-      <c r="L16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I17">
         <v>459000</v>
       </c>
-      <c r="L17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1500,50 +1417,44 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I18">
         <v>459000</v>
       </c>
-      <c r="L18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I19">
         <v>459000</v>
       </c>
-      <c r="L19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1552,102 +1463,90 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I20">
         <v>459000</v>
       </c>
-      <c r="L20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I21">
         <v>459000</v>
       </c>
-      <c r="L21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>17</v>
-      </c>
-      <c r="E22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I22">
         <v>459000</v>
       </c>
-      <c r="L22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I23">
         <v>459000</v>
       </c>
-      <c r="L23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1656,50 +1555,44 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I24">
         <v>459000</v>
       </c>
-      <c r="L24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I25">
         <v>459000</v>
       </c>
-      <c r="L25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1708,195 +1601,174 @@
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I26">
         <v>459000</v>
       </c>
-      <c r="L26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I27">
         <v>459000</v>
       </c>
-      <c r="L27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
         <v>11</v>
       </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I28">
         <v>379000</v>
       </c>
-      <c r="L28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
         <v>44</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
         <v>45</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" t="s">
-        <v>47</v>
-      </c>
       <c r="H29" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29">
         <v>299000</v>
       </c>
-      <c r="L29" t="s">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="H30" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="I30">
         <v>499000</v>
       </c>
-      <c r="L30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>17</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" t="s">
-        <v>49</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="I31">
         <v>499000</v>
       </c>
-      <c r="L31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I32">
         <v>499000</v>
       </c>
-      <c r="L32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1905,166 +1777,142 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I33">
         <v>499000</v>
       </c>
-      <c r="L33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="I34">
         <v>499000</v>
       </c>
-      <c r="L34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>17</v>
-      </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I35">
         <v>459000</v>
       </c>
-      <c r="L35" t="s">
+    </row>
+    <row r="36" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="7">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="I36" s="7">
         <v>459000</v>
       </c>
-      <c r="J36" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" t="s">
-        <v>57</v>
+        <v>144</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I37">
         <v>459000</v>
       </c>
-      <c r="L37" t="s">
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="s">
-        <v>41</v>
-      </c>
-      <c r="F38" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I38">
         <v>459000</v>
       </c>
-      <c r="L38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2073,24 +1921,21 @@
         <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I39">
         <v>399000</v>
       </c>
-      <c r="L39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2099,50 +1944,44 @@
         <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I40">
         <v>459000</v>
       </c>
-      <c r="L40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I41">
         <v>459000</v>
       </c>
-      <c r="L41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2151,24 +1990,21 @@
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I42">
         <v>459000</v>
       </c>
-      <c r="L42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2177,24 +2013,21 @@
         <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I43">
         <v>459000</v>
       </c>
-      <c r="L43" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -2203,50 +2036,44 @@
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I44">
         <v>459000</v>
       </c>
-      <c r="L44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I45">
         <v>459000</v>
       </c>
-      <c r="L45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -2255,50 +2082,44 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I46">
         <v>459000</v>
       </c>
-      <c r="L46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C47">
         <v>4</v>
       </c>
       <c r="D47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" t="s">
-        <v>19</v>
-      </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I47">
         <v>459000</v>
       </c>
-      <c r="L47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2307,76 +2128,67 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I48">
         <v>459000</v>
       </c>
-      <c r="L48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" t="s">
         <v>63</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" t="s">
-        <v>66</v>
-      </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I49">
         <v>459000</v>
       </c>
-      <c r="L49" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>17</v>
+      </c>
+      <c r="E50" t="s">
         <v>63</v>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>17</v>
-      </c>
-      <c r="E50" t="s">
-        <v>66</v>
-      </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I50">
         <v>459000</v>
       </c>
-      <c r="L50" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2385,50 +2197,44 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I51">
         <v>459000</v>
       </c>
-      <c r="L51" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
         <v>63</v>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" t="s">
-        <v>66</v>
-      </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I52">
         <v>459000</v>
       </c>
-      <c r="L52" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2437,24 +2243,21 @@
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I53">
         <v>379000</v>
       </c>
-      <c r="L53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2463,667 +2266,589 @@
         <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I54">
         <v>459000</v>
       </c>
-      <c r="L54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" t="s">
         <v>31</v>
       </c>
-      <c r="E55" t="s">
-        <v>32</v>
-      </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55">
         <v>379000</v>
       </c>
-      <c r="L55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="I56">
         <v>269000</v>
       </c>
-      <c r="L56" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I57">
         <v>299000</v>
       </c>
-      <c r="L57" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I58">
         <v>299000</v>
       </c>
-      <c r="L58" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C59" s="9">
         <v>2</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I59" s="9">
         <v>299000</v>
       </c>
-      <c r="J59" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I60">
         <v>499000</v>
       </c>
-      <c r="L60" t="s">
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I61">
         <v>379000</v>
       </c>
-      <c r="L61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" t="s">
         <v>13</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="I62">
         <v>349000</v>
       </c>
-      <c r="L62" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
         <v>19</v>
       </c>
-      <c r="F63" t="s">
-        <v>20</v>
-      </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I63">
         <v>299000</v>
       </c>
-      <c r="L63" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I64">
         <v>479000</v>
       </c>
-      <c r="L64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" t="s">
         <v>18</v>
       </c>
-      <c r="E65" t="s">
-        <v>19</v>
-      </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I65">
         <v>479000</v>
       </c>
-      <c r="L65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I66">
         <v>479000</v>
       </c>
-      <c r="L66" t="s">
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
-      </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I67">
         <v>499000</v>
       </c>
-      <c r="L67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C68" s="9">
         <v>3</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I68" s="9">
         <v>499000</v>
       </c>
-      <c r="J68" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I69">
         <v>499000</v>
       </c>
-      <c r="L69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I70">
         <v>379000</v>
       </c>
-      <c r="L70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I71">
         <v>479000</v>
       </c>
-      <c r="L71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E72" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I72">
         <v>479000</v>
       </c>
-      <c r="L72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I73">
         <v>479000</v>
       </c>
-      <c r="L73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C74">
         <v>2</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I74">
         <v>479000</v>
       </c>
-      <c r="L74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I75">
         <v>479000</v>
       </c>
-      <c r="L75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F76" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="I76">
         <v>299000</v>
       </c>
-      <c r="L76" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I77">
         <v>299000</v>
       </c>
-      <c r="L77" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -3132,24 +2857,21 @@
         <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I78">
         <v>399000</v>
       </c>
-      <c r="L78" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3158,24 +2880,21 @@
         <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I79">
         <v>399000</v>
       </c>
-      <c r="L79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -3184,102 +2903,90 @@
         <v>17</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I80">
         <v>399000</v>
       </c>
-      <c r="L80" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I81">
         <v>399000</v>
       </c>
-      <c r="L81" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I82">
         <v>399000</v>
       </c>
-      <c r="L82" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E83" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I83">
         <v>399000</v>
       </c>
-      <c r="L83" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -3288,53 +2995,44 @@
         <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I84">
         <v>399000</v>
       </c>
-      <c r="L84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C85" s="5">
         <v>1</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I85" s="5">
         <v>399000</v>
       </c>
-      <c r="J85" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L85" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3343,24 +3041,21 @@
         <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I86">
         <v>399000</v>
       </c>
-      <c r="L86" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3369,256 +3064,226 @@
         <v>16</v>
       </c>
       <c r="E87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I87">
         <v>399000</v>
       </c>
-      <c r="L87" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I88">
         <v>499000</v>
       </c>
-      <c r="L88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I89">
         <v>299000</v>
       </c>
-      <c r="L89" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E90" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I90">
         <v>299000</v>
       </c>
-      <c r="L90" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I91">
         <v>299000</v>
       </c>
-      <c r="L91" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I92">
         <v>379000</v>
       </c>
-      <c r="L92" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C93" s="5">
         <v>1</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="I93" s="5">
         <v>299000</v>
       </c>
-      <c r="J93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L93" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E94" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I94">
         <v>399000</v>
       </c>
-      <c r="L94" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I95">
         <v>399000</v>
       </c>
-      <c r="L95" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3627,56 +3292,50 @@
         <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I96">
         <v>399000</v>
       </c>
-      <c r="L96" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C97">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I97">
         <v>399000</v>
       </c>
-      <c r="L97" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3685,137 +3344,122 @@
         <v>15</v>
       </c>
       <c r="E98" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I98">
         <v>399000</v>
       </c>
-      <c r="L98" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I99">
         <v>399000</v>
       </c>
-      <c r="L99" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I100">
         <v>399000</v>
       </c>
-      <c r="L100" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I101">
         <v>399000</v>
       </c>
-      <c r="L101" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I102">
         <v>399000</v>
       </c>
-      <c r="L102" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -3824,24 +3468,21 @@
         <v>16</v>
       </c>
       <c r="E103" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103">
         <v>399000</v>
       </c>
-      <c r="L103" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -3850,50 +3491,44 @@
         <v>15</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I104">
         <v>399000</v>
       </c>
-      <c r="L104" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C105">
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I105">
         <v>499000</v>
       </c>
-      <c r="L105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -3902,50 +3537,44 @@
         <v>16</v>
       </c>
       <c r="E106" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I106">
         <v>499000</v>
       </c>
-      <c r="L106" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E107" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I107">
         <v>499000</v>
       </c>
-      <c r="L107" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -3954,305 +3583,272 @@
         <v>17</v>
       </c>
       <c r="E108" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I108">
         <v>499000</v>
       </c>
-      <c r="L108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109" t="s">
+        <v>63</v>
+      </c>
+      <c r="F109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E109" t="s">
-        <v>66</v>
-      </c>
-      <c r="F109" t="s">
-        <v>22</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I109">
         <v>499000</v>
       </c>
-      <c r="L109" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E110" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I110">
         <v>499000</v>
       </c>
-      <c r="L110" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" t="s">
+        <v>108</v>
+      </c>
+      <c r="F111" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E111" t="s">
-        <v>112</v>
-      </c>
-      <c r="F111" t="s">
-        <v>22</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I111">
         <v>499000</v>
       </c>
-      <c r="L111" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C112">
         <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E112" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I112">
         <v>499000</v>
       </c>
-      <c r="L112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I113">
         <v>299000</v>
       </c>
-      <c r="L113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E114" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I114">
         <v>299000</v>
       </c>
-      <c r="L114" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E115" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I115">
         <v>299000</v>
       </c>
-      <c r="L115" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I116">
         <v>299000</v>
       </c>
-      <c r="L116" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E117" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I117">
         <v>499000</v>
       </c>
-      <c r="L117" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F118" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I118">
         <v>499000</v>
       </c>
-      <c r="L118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -4261,24 +3857,21 @@
         <v>17</v>
       </c>
       <c r="E119" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I119">
         <v>499000</v>
       </c>
-      <c r="L119" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -4287,50 +3880,44 @@
         <v>16</v>
       </c>
       <c r="E120" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I120">
         <v>499000</v>
       </c>
-      <c r="L120" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E121" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I121">
         <v>499000</v>
       </c>
-      <c r="L121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -4339,206 +3926,182 @@
         <v>17</v>
       </c>
       <c r="E122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I122">
         <v>399000</v>
       </c>
-      <c r="L122" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F123" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I123">
         <v>499000</v>
       </c>
-      <c r="L123" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F124" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I124">
         <v>499000</v>
       </c>
-      <c r="L124" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E125" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I125">
         <v>379000</v>
       </c>
-      <c r="L125" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E126" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I126">
         <v>399000</v>
       </c>
-      <c r="L126" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C127">
         <v>1</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I127">
         <v>379000</v>
       </c>
-      <c r="L127" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F128" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I128">
         <v>379000</v>
       </c>
-      <c r="L128" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E129" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I129">
         <v>379000</v>
       </c>
-      <c r="L129" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4547,50 +4110,44 @@
         <v>17</v>
       </c>
       <c r="E130" t="s">
+        <v>18</v>
+      </c>
+      <c r="F130" t="s">
         <v>19</v>
       </c>
-      <c r="F130" t="s">
-        <v>20</v>
-      </c>
       <c r="H130" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I130">
         <v>379000</v>
       </c>
-      <c r="L130" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C131">
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E131" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F131" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I131">
         <v>459000</v>
       </c>
-      <c r="L131" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4599,76 +4156,67 @@
         <v>17</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I132">
         <v>459000</v>
       </c>
-      <c r="L132" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C133">
         <v>3</v>
       </c>
       <c r="D133" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E133" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F133" t="s">
+        <v>36</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I133">
         <v>459000</v>
       </c>
-      <c r="L133" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E134" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F134" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I134">
         <v>459000</v>
       </c>
-      <c r="L134" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -4677,45 +4225,39 @@
         <v>15</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F135" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I135">
         <v>459000</v>
       </c>
-      <c r="L135" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C136">
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I136">
         <v>459000</v>
-      </c>
-      <c r="L136" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4742,13 +4284,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B2" s="11">
         <v>1100000</v>
@@ -4756,7 +4298,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11">
         <v>200000</v>
@@ -4764,7 +4306,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -4772,7 +4314,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B7" s="11">
         <v>400239</v>
@@ -4782,7 +4324,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B8" s="11">
         <v>70000</v>
@@ -4791,19 +4333,19 @@
         <v>15000</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B12" s="11">
         <v>200000</v>
@@ -4812,7 +4354,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B13" s="11">
         <v>200000</v>
@@ -4821,7 +4363,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B14" s="11">
         <v>200000</v>
@@ -4830,7 +4372,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B15" s="11">
         <v>321300</v>
@@ -4841,7 +4383,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B16" s="11">
         <v>255000</v>
@@ -4851,7 +4393,7 @@
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B19" s="18">
         <v>1915239</v>
@@ -4859,7 +4401,7 @@
     </row>
     <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B20" s="18">
         <v>1455600</v>
@@ -4867,7 +4409,7 @@
     </row>
     <row r="21" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B21" s="18">
         <v>-459639</v>
